--- a/Employee_Reports_wi52/Gomer Repaso Plenos Q0385.xlsx
+++ b/Employee_Reports_wi52/Gomer Repaso Plenos Q0385.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1181,53 +1181,53 @@
       <c r="K15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Cool Room (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>LSME-CRG-M-011</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2024</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>29-Sep-2026</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1448,11 +1448,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-39</v>
+        <v>-47</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="5" t="n">
-        <v>-37</v>
+        <v>-45</v>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-133</v>
+        <v>-141</v>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -1829,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-132</v>
+        <v>-140</v>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="5" t="n">
-        <v>-33</v>
+        <v>-41</v>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
@@ -1976,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="5" t="n">
-        <v>-26</v>
+        <v>-34</v>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
@@ -2025,11 +2025,11 @@
         </is>
       </c>
       <c r="H33" s="5" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
@@ -2062,11 +2062,11 @@
         </is>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-27</v>
+        <v>-35</v>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
@@ -2077,41 +2077,41 @@
       <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr"/>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2025</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
         <is>
           <t>30-Sep-2026</t>
         </is>
       </c>
-      <c r="H35" s="3" t="n">
-        <v>41</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr"/>
+      <c r="H35" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="n">
@@ -2148,11 +2148,11 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>-5</v>
+        <v>-13</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2234,11 +2234,11 @@
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -2271,11 +2271,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2308,11 +2308,11 @@
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -2345,11 +2345,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -2382,11 +2382,11 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -2419,11 +2419,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>727</v>
+        <v>719</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7991</v>
+        <v>7983</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7927</v>
+        <v>7919</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3267,7 +3267,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7984</v>
+        <v>7976</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7985</v>
+        <v>7977</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3354,7 +3354,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7924</v>
+        <v>7916</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7925</v>
+        <v>7917</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7928</v>
+        <v>7920</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
